--- a/CBAR_Gold_Rates.xlsx
+++ b/CBAR_Gold_Rates.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B706"/>
+  <dimension ref="A1:B707"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7490,6 +7490,16 @@
         <v>7363.8985</v>
       </c>
     </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>14.09.2026</t>
+        </is>
+      </c>
+      <c r="B707" t="n">
+        <v>7360.303</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CBAR_Gold_Rates.xlsx
+++ b/CBAR_Gold_Rates.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B707"/>
+  <dimension ref="A1:B708"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7500,6 +7500,16 @@
         <v>7360.303</v>
       </c>
     </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>15.09.2026</t>
+        </is>
+      </c>
+      <c r="B708" t="n">
+        <v>7318.857</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CBAR_Gold_Rates.xlsx
+++ b/CBAR_Gold_Rates.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B708"/>
+  <dimension ref="A1:B709"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7510,6 +7510,16 @@
         <v>7318.857</v>
       </c>
     </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>16.09.2026</t>
+        </is>
+      </c>
+      <c r="B709" t="n">
+        <v>7347.264</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CBAR_Gold_Rates.xlsx
+++ b/CBAR_Gold_Rates.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B709"/>
+  <dimension ref="A1:B710"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7520,6 +7520,16 @@
         <v>7347.264</v>
       </c>
     </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>17.09.2026</t>
+        </is>
+      </c>
+      <c r="B710" t="n">
+        <v>7305.3505</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CBAR_Gold_Rates.xlsx
+++ b/CBAR_Gold_Rates.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B710"/>
+  <dimension ref="A1:B711"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7530,6 +7530,16 @@
         <v>7305.3505</v>
       </c>
     </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>18.09.2026</t>
+        </is>
+      </c>
+      <c r="B711" t="n">
+        <v>7423.934</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CBAR_Gold_Rates.xlsx
+++ b/CBAR_Gold_Rates.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B711"/>
+  <dimension ref="A1:B712"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7540,6 +7540,16 @@
         <v>7423.934</v>
       </c>
     </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B712" t="n">
+        <v>7404.741</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CBAR_Gold_Rates.xlsx
+++ b/CBAR_Gold_Rates.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B712"/>
+  <dimension ref="A1:B713"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7550,6 +7550,16 @@
         <v>7404.741</v>
       </c>
     </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>22.09.2026</t>
+        </is>
+      </c>
+      <c r="B713" t="n">
+        <v>7380.7625</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CBAR_Gold_Rates.xlsx
+++ b/CBAR_Gold_Rates.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B713"/>
+  <dimension ref="A1:B714"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7560,6 +7560,16 @@
         <v>7380.7625</v>
       </c>
     </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>23.09.2026</t>
+        </is>
+      </c>
+      <c r="B714" t="n">
+        <v>7384.6725</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CBAR_Gold_Rates.xlsx
+++ b/CBAR_Gold_Rates.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B714"/>
+  <dimension ref="A1:B716"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7570,6 +7570,26 @@
         <v>7384.6725</v>
       </c>
     </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>24.09.2026</t>
+        </is>
+      </c>
+      <c r="B715" t="n">
+        <v>7294.853</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>25.09.2026</t>
+        </is>
+      </c>
+      <c r="B716" t="n">
+        <v>7245.9355</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CBAR_Gold_Rates.xlsx
+++ b/CBAR_Gold_Rates.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B716"/>
+  <dimension ref="A1:B717"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7590,6 +7590,16 @@
         <v>7245.9355</v>
       </c>
     </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B717" t="n">
+        <v>7133.064</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CBAR_Gold_Rates.xlsx
+++ b/CBAR_Gold_Rates.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B717"/>
+  <dimension ref="A1:B718"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7600,6 +7600,16 @@
         <v>7133.064</v>
       </c>
     </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="B718" t="n">
+        <v>7015.305</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CBAR_Gold_Rates.xlsx
+++ b/CBAR_Gold_Rates.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B718"/>
+  <dimension ref="A1:B719"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7610,6 +7610,16 @@
         <v>7015.305</v>
       </c>
     </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="B719" t="n">
+        <v>7104.555</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CBAR_Gold_Rates.xlsx
+++ b/CBAR_Gold_Rates.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B719"/>
+  <dimension ref="A1:B720"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7620,6 +7620,16 @@
         <v>7104.555</v>
       </c>
     </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>01.10.2026</t>
+        </is>
+      </c>
+      <c r="B720" t="n">
+        <v>7106.1105</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CBAR_Gold_Rates.xlsx
+++ b/CBAR_Gold_Rates.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B720"/>
+  <dimension ref="A1:B721"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7630,6 +7630,16 @@
         <v>7106.1105</v>
       </c>
     </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>02.10.2026</t>
+        </is>
+      </c>
+      <c r="B721" t="n">
+        <v>7114.3555</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CBAR_Gold_Rates.xlsx
+++ b/CBAR_Gold_Rates.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B721"/>
+  <dimension ref="A1:B722"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7640,6 +7640,16 @@
         <v>7114.3555</v>
       </c>
     </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>05.10.2026</t>
+        </is>
+      </c>
+      <c r="B722" t="n">
+        <v>7025.2755</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CBAR_Gold_Rates.xlsx
+++ b/CBAR_Gold_Rates.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B722"/>
+  <dimension ref="A1:B723"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7650,6 +7650,16 @@
         <v>7025.2755</v>
       </c>
     </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>06.10.2026</t>
+        </is>
+      </c>
+      <c r="B723" t="n">
+        <v>7007.74</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CBAR_Gold_Rates.xlsx
+++ b/CBAR_Gold_Rates.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B723"/>
+  <dimension ref="A1:B724"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7660,6 +7660,16 @@
         <v>7007.74</v>
       </c>
     </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>07.10.2026</t>
+        </is>
+      </c>
+      <c r="B724" t="n">
+        <v>7029.67</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CBAR_Gold_Rates.xlsx
+++ b/CBAR_Gold_Rates.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B724"/>
+  <dimension ref="A1:B725"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7670,6 +7670,16 @@
         <v>7029.67</v>
       </c>
     </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>08.10.2026</t>
+        </is>
+      </c>
+      <c r="B725" t="n">
+        <v>7025.692</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CBAR_Gold_Rates.xlsx
+++ b/CBAR_Gold_Rates.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B725"/>
+  <dimension ref="A1:B726"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7680,6 +7680,16 @@
         <v>7025.692</v>
       </c>
     </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>09.10.2026</t>
+        </is>
+      </c>
+      <c r="B726" t="n">
+        <v>7112.1285</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CBAR_Gold_Rates.xlsx
+++ b/CBAR_Gold_Rates.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B726"/>
+  <dimension ref="A1:B727"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7690,6 +7690,16 @@
         <v>7112.1285</v>
       </c>
     </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>12.10.2026</t>
+        </is>
+      </c>
+      <c r="B727" t="n">
+        <v>7132.9705</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CBAR_Gold_Rates.xlsx
+++ b/CBAR_Gold_Rates.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B727"/>
+  <dimension ref="A1:B728"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7700,6 +7700,16 @@
         <v>7132.9705</v>
       </c>
     </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>13.10.2026</t>
+        </is>
+      </c>
+      <c r="B728" t="n">
+        <v>7133.251</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CBAR_Gold_Rates.xlsx
+++ b/CBAR_Gold_Rates.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B728"/>
+  <dimension ref="A1:B729"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7710,6 +7710,16 @@
         <v>7133.251</v>
       </c>
     </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>14.10.2026</t>
+        </is>
+      </c>
+      <c r="B729" t="n">
+        <v>7080.9675</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CBAR_Gold_Rates.xlsx
+++ b/CBAR_Gold_Rates.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B729"/>
+  <dimension ref="A1:B730"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7720,6 +7720,16 @@
         <v>7080.9675</v>
       </c>
     </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>15.10.2026</t>
+        </is>
+      </c>
+      <c r="B730" t="n">
+        <v>7046.8995</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CBAR_Gold_Rates.xlsx
+++ b/CBAR_Gold_Rates.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B730"/>
+  <dimension ref="A1:B731"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7730,6 +7730,16 @@
         <v>7046.8995</v>
       </c>
     </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>16.10.2026</t>
+        </is>
+      </c>
+      <c r="B731" t="n">
+        <v>7096.6415</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CBAR_Gold_Rates.xlsx
+++ b/CBAR_Gold_Rates.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,16 +413,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B731"/>
+  <dimension ref="A1:B739"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Tarix</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>XAU_Qiymeti</t>
         </is>
@@ -7738,6 +7726,86 @@
       </c>
       <c r="B731" t="n">
         <v>7096.6415</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>19.10.2026</t>
+        </is>
+      </c>
+      <c r="B732" t="n">
+        <v>7111.355</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="B733" t="n">
+        <v>7044.5025</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>21.10.2026</t>
+        </is>
+      </c>
+      <c r="B734" t="n">
+        <v>6995.4575</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>22.10.2026</t>
+        </is>
+      </c>
+      <c r="B735" t="n">
+        <v>6954.462</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>23.10.2026</t>
+        </is>
+      </c>
+      <c r="B736" t="n">
+        <v>6809.401</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="B737" t="n">
+        <v>6827.421</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>27.10.2026</t>
+        </is>
+      </c>
+      <c r="B738" t="n">
+        <v>6818.7085</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>28.10.2026</t>
+        </is>
+      </c>
+      <c r="B739" t="n">
+        <v>6862.5005</v>
       </c>
     </row>
   </sheetData>

--- a/CBAR_Gold_Rates.xlsx
+++ b/CBAR_Gold_Rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B739"/>
+  <dimension ref="A1:B740"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7808,6 +7808,16 @@
         <v>6862.5005</v>
       </c>
     </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>29.10.2026</t>
+        </is>
+      </c>
+      <c r="B740" t="n">
+        <v>6867.881</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CBAR_Gold_Rates.xlsx
+++ b/CBAR_Gold_Rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B740"/>
+  <dimension ref="A1:B741"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7818,6 +7818,16 @@
         <v>6867.881</v>
       </c>
     </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>30.10.2026</t>
+        </is>
+      </c>
+      <c r="B741" t="n">
+        <v>6796.43</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
